--- a/Team-Data/2008-09/4-2-2008-09.xlsx
+++ b/Team-Data/2008-09/4-2-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -775,7 +842,7 @@
         <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -793,7 +860,7 @@
         <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,10 +928,10 @@
         <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -873,28 +940,28 @@
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
@@ -903,7 +970,7 @@
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -915,13 +982,13 @@
         <v>22.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -954,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -981,10 +1048,10 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1178,7 +1245,7 @@
         <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
@@ -1276,19 +1343,19 @@
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>7</v>
@@ -1318,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1348,19 +1415,19 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -1404,28 +1471,28 @@
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
         <v>0.755</v>
@@ -1434,19 +1501,19 @@
         <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T6" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
         <v>5.4</v>
@@ -1458,10 +1525,10 @@
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
         <v>9.300000000000001</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,19 +1558,19 @@
         <v>6</v>
       </c>
       <c r="AL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN6" t="n">
         <v>3</v>
       </c>
-      <c r="AM6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2</v>
-      </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
@@ -1521,10 +1588,10 @@
         <v>23</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.658</v>
+        <v>0.653</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J8" t="n">
         <v>79.3</v>
@@ -1777,19 +1844,19 @@
         <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.758</v>
@@ -1798,40 +1865,40 @@
         <v>11.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T8" t="n">
         <v>41.5</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1855,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
@@ -1873,10 +1940,10 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -1894,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
@@ -1903,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2025,7 +2092,7 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2055,13 +2122,13 @@
         <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2088,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2404,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>8</v>
@@ -2431,7 +2498,7 @@
         <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2440,13 +2507,13 @@
         <v>25</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2583,7 +2650,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2619,7 +2686,7 @@
         <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,10 +2695,10 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2771,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2795,7 +2862,7 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2807,13 +2874,13 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>30</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
@@ -2872,31 +2939,31 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P14" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
@@ -2905,25 +2972,25 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>107.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2950,7 +3017,7 @@
         <v>14</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
         <v>18</v>
@@ -2959,10 +3026,10 @@
         <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2980,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3208,7 @@
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3476,7 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.443</v>
@@ -3421,31 +3488,31 @@
         <v>16.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
         <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3454,13 +3521,13 @@
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z17" t="n">
         <v>24.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
         <v>98.90000000000001</v>
@@ -3469,7 +3536,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3499,13 +3566,13 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3523,10 +3590,10 @@
         <v>8</v>
       </c>
       <c r="AV17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW17" t="n">
         <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3675,10 +3742,10 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
@@ -3687,10 +3754,10 @@
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3857,7 +3924,7 @@
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
@@ -3869,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3893,16 +3960,16 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4021,10 +4088,10 @@
         <v>8</v>
       </c>
       <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>9</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4069,7 +4136,7 @@
         <v>28</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>15</v>
@@ -4081,10 +4148,10 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4212,7 +4279,7 @@
         <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4491,7 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>26</v>
@@ -4594,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4615,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
         <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>0.527</v>
+        <v>0.521</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
         <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="P24" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.748</v>
@@ -4710,7 +4777,7 @@
         <v>12.6</v>
       </c>
       <c r="S24" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T24" t="n">
         <v>41.4</v>
@@ -4719,34 +4786,34 @@
         <v>20.3</v>
       </c>
       <c r="V24" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W24" t="n">
         <v>8.1</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AE24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
@@ -4758,13 +4825,13 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4791,25 +4858,25 @@
         <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
         <v>22</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4985,7 +5052,7 @@
         <v>20</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
         <v>47</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.644</v>
+        <v>0.635</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
         <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5077,13 +5144,13 @@
         <v>28.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5095,34 +5162,34 @@
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>16</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>13</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,13 +5222,13 @@
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5371,7 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
         <v>46</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.613</v>
+        <v>0.622</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,10 +5842,10 @@
         <v>38.5</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.475</v>
+        <v>0.477</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5790,25 +5857,25 @@
         <v>0.349</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
         <v>29.7</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5820,22 +5887,22 @@
         <v>4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB30" t="n">
         <v>103.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="n">
         <v>10</v>
@@ -5847,10 +5914,10 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
         <v>15</v>
@@ -5874,31 +5941,31 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
         <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5910,7 +5977,7 @@
         <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
@@ -5939,46 +6006,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
         <v>59</v>
       </c>
       <c r="G31" t="n">
-        <v>0.234</v>
+        <v>0.224</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.329</v>
+        <v>0.331</v>
       </c>
       <c r="O31" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P31" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
@@ -5987,40 +6054,40 @@
         <v>28.2</v>
       </c>
       <c r="T31" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U31" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V31" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
         <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>30</v>
@@ -6032,7 +6099,7 @@
         <v>30</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6056,7 +6123,7 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6080,7 +6147,7 @@
         <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ31" t="n">
         <v>13</v>
@@ -6089,7 +6156,7 @@
         <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2008-09</t>
+          <t>2009-04-02</t>
         </is>
       </c>
     </row>
